--- a/backtest_runs/20260410_193731/by_symbol/SCL/SCL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/SCL/SCL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         <v>-2605.170000000003</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>109538.23</v>
@@ -863,7 +863,7 @@
         <v>-5772</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>106771</v>
@@ -955,7 +955,7 @@
         <v>-5533.350000000002</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>101252.08</v>
@@ -1139,7 +1139,7 @@
         <v>-609.390000000001</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>111389.71</v>
@@ -1185,7 +1185,7 @@
         <v>-4457.759999999997</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>106931.95</v>
@@ -1277,7 +1277,7 @@
         <v>-602.7299999999944</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>110053.27</v>
@@ -1323,7 +1323,7 @@
         <v>-3197.910000000007</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>106855.36</v>
@@ -1415,7 +1415,7 @@
         <v>-979.0200000000056</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>106901.98</v>
@@ -1507,7 +1507,7 @@
         <v>-1298.700000000005</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>105805.3</v>
